--- a/data.xlsx
+++ b/data.xlsx
@@ -5,7 +5,7 @@
   <workbookPr defaultThemeVersion="164011"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Kne\Desktop\AI\어플-모바일업체조회\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Kne\Desktop\AI\어플-모바일업체조회\files\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15933" uniqueCount="7630">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15935" uniqueCount="7633">
   <si>
     <t>업체명</t>
   </si>
@@ -22916,6 +22916,18 @@
   </si>
   <si>
     <t>himpel@himpel.com</t>
+  </si>
+  <si>
+    <t>R-6</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>R-5</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>R-4</t>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -34604,7 +34616,9 @@
       <c r="L221" s="3" t="s">
         <v>52</v>
       </c>
-      <c r="M221" s="3"/>
+      <c r="M221" s="3" t="s">
+        <v>7632</v>
+      </c>
       <c r="N221" s="3" t="s">
         <v>340</v>
       </c>
@@ -37816,7 +37830,7 @@
         <v>81</v>
       </c>
       <c r="M284" s="3" t="s">
-        <v>1407</v>
+        <v>7631</v>
       </c>
       <c r="N284" s="3" t="s">
         <v>63</v>
@@ -39974,7 +39988,7 @@
         <v>81</v>
       </c>
       <c r="M326" s="3" t="s">
-        <v>122</v>
+        <v>7630</v>
       </c>
       <c r="N326" s="3" t="s">
         <v>534</v>
@@ -77229,7 +77243,9 @@
       <c r="L1056" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="M1056" s="3"/>
+      <c r="M1056" s="3" t="s">
+        <v>7630</v>
+      </c>
       <c r="N1056" s="3" t="s">
         <v>453</v>
       </c>
@@ -77281,7 +77297,7 @@
         <v>81</v>
       </c>
       <c r="M1057" s="3" t="s">
-        <v>122</v>
+        <v>7632</v>
       </c>
       <c r="N1057" s="3" t="s">
         <v>162</v>
@@ -77677,7 +77693,7 @@
         <v>114</v>
       </c>
       <c r="M1065" s="3" t="s">
-        <v>122</v>
+        <v>7632</v>
       </c>
       <c r="N1065" s="3" t="s">
         <v>492</v>
@@ -89405,7 +89421,7 @@
         <v>34</v>
       </c>
       <c r="M1297" s="3" t="s">
-        <v>122</v>
+        <v>7630</v>
       </c>
       <c r="N1297" s="3" t="s">
         <v>1193</v>
@@ -95136,5 +95152,6 @@
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
--- a/data.xlsx
+++ b/data.xlsx
@@ -3394,6 +3394,9 @@
       <c r="L60" t="str">
         <v>C+</v>
       </c>
+      <c r="M60" t="str">
+        <v>R-3</v>
+      </c>
       <c r="N60" t="str">
         <v>광주광역시 북구</v>
       </c>
@@ -12697,31 +12700,34 @@
         <v>25년(정규)</v>
       </c>
       <c r="D247">
-        <v>24540</v>
+        <v>24539</v>
       </c>
       <c r="E247">
-        <v>23.572</v>
+        <v>23.6</v>
+      </c>
+      <c r="F247">
+        <v>0</v>
       </c>
       <c r="G247" t="str">
         <v>기계설비공사</v>
       </c>
       <c r="H247">
-        <v>33051290</v>
+        <v>29904820</v>
       </c>
       <c r="I247" t="str">
         <v>기계설비공사업, 소방시설공사업</v>
       </c>
       <c r="J247" t="str">
-        <v>더시너지2(주), 롯데건설(주), 쌍용건설(주), 코오롱글로벌(주), 해군군수사령부지출관</v>
+        <v>롯데건설(주), 쌍용건설(주), 더시너지2(주), 넥스트브이시티피에프브이(주), (주)금성백조건설</v>
       </c>
       <c r="K247" t="str">
-        <v>BB0</v>
+        <v>BB+</v>
       </c>
       <c r="L247" t="str">
-        <v>C+(CFR3)</v>
+        <v>C+</v>
       </c>
       <c r="M247" t="str">
-        <v>NRM4</v>
+        <v>R-2</v>
       </c>
       <c r="N247" t="str">
         <v>대전광역시 대덕구</v>
@@ -36500,6 +36506,9 @@
       <c r="L722" t="str">
         <v>A</v>
       </c>
+      <c r="M722" t="str">
+        <v>R-2</v>
+      </c>
       <c r="N722" t="str">
         <v>경상북도 경산시</v>
       </c>
@@ -42636,6 +42645,9 @@
       </c>
       <c r="L846" t="str">
         <v>A</v>
+      </c>
+      <c r="M846" t="str">
+        <v>R-3</v>
       </c>
       <c r="N846" t="str">
         <v>인천광역시 남동구</v>

--- a/data.xlsx
+++ b/data.xlsx
@@ -1648,7 +1648,7 @@
         <v>비계,구조물해체공사업, 습식방수공사업, 철근,콘크리트공사업</v>
       </c>
       <c r="J25" t="str">
-        <v>두산건설 주식회사, (주)포스코이앤씨, 두산에너빌리티 (주), 지에스건설（주）, 롯데건설（주）</v>
+        <v>(주)포스코이앤씨, 두산건설 주식회사, 두산에너빌리티 (주), 롯데건설（주）, 지에스건설（주）</v>
       </c>
       <c r="K25" t="str">
         <v>BB+</v>
@@ -3471,25 +3471,31 @@
         <v>25년(예비)</v>
       </c>
       <c r="D62">
-        <v>2074</v>
+        <v>3781</v>
       </c>
       <c r="E62">
-        <v>15.7</v>
-      </c>
-      <c r="F62">
-        <v>0.4</v>
+        <v>12.66</v>
+      </c>
+      <c r="G62" t="str">
+        <v>하자보수공사</v>
+      </c>
+      <c r="H62">
+        <v>4362776</v>
       </c>
       <c r="I62" t="str">
-        <v>토공사업, 토목공사업, 포장공사업</v>
+        <v>시설물유지관리업, 토공사업, 토목공사업, 포장공사업</v>
       </c>
       <c r="J62" t="str">
-        <v>경상북도울릉군청, 경상북도김천시청, 경상북도북부건설사업소, 경상북도청송군청, 경상북도김천교육지원청</v>
+        <v>디엘이앤씨 주식회사, 울릉군청, 청송군청, 김천시청, (주)성풍이앤에이</v>
       </c>
       <c r="K62" t="str">
-        <v>B+</v>
+        <v>BB-</v>
       </c>
       <c r="L62" t="str">
-        <v>C+</v>
+        <v>B(CFR2)</v>
+      </c>
+      <c r="M62" t="str">
+        <v>NRM3</v>
       </c>
       <c r="N62" t="str">
         <v>경상북도 김천시</v>
@@ -18217,7 +18223,7 @@
         <v>C-</v>
       </c>
       <c r="M355" t="str">
-        <v>R-1</v>
+        <v>R-2</v>
       </c>
       <c r="N355" t="str">
         <v>충청북도 청주시</v>
@@ -26245,6 +26251,9 @@
       <c r="L516" t="str">
         <v>C-</v>
       </c>
+      <c r="M516" t="str">
+        <v>R-4</v>
+      </c>
       <c r="N516" t="str">
         <v>광주광역시 동구</v>
       </c>
@@ -29630,6 +29639,9 @@
       <c r="L584" t="str">
         <v>C+</v>
       </c>
+      <c r="M584" t="str">
+        <v>R-5</v>
+      </c>
       <c r="N584" t="str">
         <v>경상남도 김해시</v>
       </c>
@@ -44015,7 +44027,7 @@
         <v>A</v>
       </c>
       <c r="M873" t="str">
-        <v>R-1</v>
+        <v>R-2</v>
       </c>
       <c r="N873" t="str">
         <v>울산광역시 울주군</v>
@@ -52100,7 +52112,7 @@
         <v>B</v>
       </c>
       <c r="M1032" t="str">
-        <v>R-2</v>
+        <v>R-1</v>
       </c>
       <c r="N1032" t="str">
         <v>서울특별시 송파구</v>
@@ -55681,6 +55693,9 @@
       <c r="L1104" t="str">
         <v>C+</v>
       </c>
+      <c r="M1104" t="str">
+        <v>R-1</v>
+      </c>
       <c r="N1104" t="str">
         <v>대전광역시 유성구</v>
       </c>
@@ -57822,6 +57837,9 @@
       </c>
       <c r="L1146" t="str">
         <v>B</v>
+      </c>
+      <c r="M1146" t="str">
+        <v>R-4</v>
       </c>
       <c r="N1146" t="str">
         <v>광주광역시 북구</v>

--- a/data.xlsx
+++ b/data.xlsx
@@ -2968,7 +2968,7 @@
         <v>가스시설시공업1종, 기계설비공사업, 난방시공업제1종</v>
       </c>
       <c r="J52" t="str">
-        <v>주식회사 경동폴리움, 에스케이인텔릭스(주), （주）신진수도, （주）세훈SOS, 주식회사 제이케이인터내셔널</v>
+        <v>（주）세훈SOS, （주）신진수도, 에스케이인텔릭스(주), 주식회사 경동폴리움, 주식회사 제이케이인터내셔널</v>
       </c>
       <c r="K52" t="str">
         <v>AA+</v>
@@ -11259,6 +11259,9 @@
       <c r="L217" t="str">
         <v>A</v>
       </c>
+      <c r="M217" t="str">
+        <v>R-1</v>
+      </c>
       <c r="N217" t="str">
         <v>서울특별시 금천구</v>
       </c>
@@ -11862,6 +11865,9 @@
       <c r="L229" t="str">
         <v>A</v>
       </c>
+      <c r="M229" t="str">
+        <v>R-3</v>
+      </c>
       <c r="N229" t="str">
         <v>경기도 부천시</v>
       </c>
@@ -13574,13 +13580,13 @@
         <v>25년(정규)</v>
       </c>
       <c r="D264">
-        <v>4022</v>
+        <v>6428</v>
       </c>
       <c r="E264">
-        <v>29.1</v>
+        <v>24.6</v>
       </c>
       <c r="F264">
-        <v>9</v>
+        <v>8.2</v>
       </c>
       <c r="G264" t="str">
         <v>전기설비공사</v>
@@ -13592,19 +13598,19 @@
         <v>소방시설공사업, 전기공사업</v>
       </c>
       <c r="J264" t="str">
-        <v>엘쓰리일렉트릭파워(주), 경남기업(주), (주)아이마켓코리아, 제주특별자치도 상하수도본부, (주)피앤피</v>
+        <v>경남기업(주), (주)이지차저, 한국전력공사, 에이치제이매그놀리아용평디오션호텔앤리조트(주), (주)대연전력기술</v>
       </c>
       <c r="K264" t="str">
-        <v>BB-</v>
+        <v>BB+</v>
       </c>
       <c r="L264" t="str">
-        <v>C+</v>
+        <v>B</v>
       </c>
       <c r="M264" t="str">
         <v>R-3</v>
       </c>
       <c r="N264" t="str">
-        <v>전라남도 순천시</v>
+        <v>전라남도 여수시</v>
       </c>
       <c r="O264" t="str">
         <v>김용득 부장(입찰담당)</v>
@@ -16542,6 +16548,9 @@
       <c r="L322" t="str">
         <v>B</v>
       </c>
+      <c r="M322" t="str">
+        <v>R-2</v>
+      </c>
       <c r="N322" t="str">
         <v>경기도 용인시</v>
       </c>
@@ -24160,6 +24169,9 @@
       <c r="L474" t="str">
         <v>A</v>
       </c>
+      <c r="M474" t="str">
+        <v>R-4</v>
+      </c>
       <c r="N474" t="str">
         <v>서울특별시 금천구</v>
       </c>
@@ -28931,7 +28943,7 @@
         <v>C+(CFR3)</v>
       </c>
       <c r="M570" t="str">
-        <v>NRM4</v>
+        <v>NRM5</v>
       </c>
       <c r="N570" t="str">
         <v>경기도 수원시</v>
@@ -32656,6 +32668,9 @@
       <c r="L645" t="str">
         <v>B</v>
       </c>
+      <c r="M645" t="str">
+        <v>R-1</v>
+      </c>
       <c r="N645" t="str">
         <v>전라남도 여수시</v>
       </c>
@@ -34040,7 +34055,7 @@
         <v>R-4</v>
       </c>
       <c r="N672" t="str">
-        <v>서울 양천구</v>
+        <v>경기 용인시</v>
       </c>
       <c r="O672" t="str">
         <v>김남혁 부장(입찰담당)</v>
@@ -37121,6 +37136,9 @@
       <c r="L734" t="str">
         <v>A</v>
       </c>
+      <c r="M734" t="str">
+        <v>R-4</v>
+      </c>
       <c r="N734" t="str">
         <v>경기도 이천시</v>
       </c>
@@ -39652,6 +39670,9 @@
       <c r="L786" t="str">
         <v>C-</v>
       </c>
+      <c r="M786" t="str">
+        <v>R-6</v>
+      </c>
       <c r="N786" t="str">
         <v>서울특별시 송파구</v>
       </c>
@@ -40505,10 +40526,10 @@
         <v>25년(정규)</v>
       </c>
       <c r="D804">
-        <v>5324</v>
+        <v>8427</v>
       </c>
       <c r="E804">
-        <v>12.4</v>
+        <v>11.5</v>
       </c>
       <c r="F804">
         <v>0</v>
@@ -40523,13 +40544,13 @@
         <v>상,하수도설비공사업, 철근,콘크리트공사업, 토공사업</v>
       </c>
       <c r="J804" t="str">
-        <v>일진건설산업(주), 농협네트웍스, 남화토건(주), (주)강원건설, (주)이테크건설</v>
+        <v>(주)농협네트웍스, 성남시분당구청, (주)강원건설, (유)성우이앤씨, 대연상사</v>
       </c>
       <c r="K804" t="str">
-        <v>BB-(만료)</v>
+        <v>BB-</v>
       </c>
       <c r="L804" t="str">
-        <v>B</v>
+        <v>A</v>
       </c>
       <c r="M804" t="str">
         <v>R-4</v>
@@ -41394,7 +41415,7 @@
         <v>B</v>
       </c>
       <c r="M821" t="str">
-        <v>R-1</v>
+        <v>R-2</v>
       </c>
       <c r="N821" t="str">
         <v>서울특별시 송파구</v>
@@ -41769,15 +41790,6 @@
       <c r="C829" t="str">
         <v>25년(예비)</v>
       </c>
-      <c r="D829">
-        <v>770</v>
-      </c>
-      <c r="E829">
-        <v>283.9</v>
-      </c>
-      <c r="F829">
-        <v>20.3</v>
-      </c>
       <c r="K829" t="str">
         <v>B-</v>
       </c>
@@ -43459,7 +43471,7 @@
         <v>C+(CFR3)</v>
       </c>
       <c r="M862" t="str">
-        <v>NRM6</v>
+        <v>NRM5</v>
       </c>
       <c r="N862" t="str">
         <v>경상북도 구미시</v>
@@ -45369,10 +45381,7 @@
         <v>전라남도 여수시</v>
       </c>
       <c r="O899" t="str">
-        <v>서은하</v>
-      </c>
-      <c r="P899" t="str">
-        <v>010-2996-4537</v>
+        <v>노은선 차장</v>
       </c>
       <c r="Q899" t="str">
         <v>wooju@wjconst.kr</v>
@@ -48293,6 +48302,9 @@
       <c r="L956" t="str">
         <v>A</v>
       </c>
+      <c r="M956" t="str">
+        <v>R-1</v>
+      </c>
       <c r="N956" t="str">
         <v>대전광역시 유성구</v>
       </c>
@@ -55153,7 +55165,7 @@
         <v>엔지니어링활동주체신고증</v>
       </c>
       <c r="J1093" t="str">
-        <v>삼환기업(주), 나라장터(조달청) 및 기타, 기후에너지환경부 원주지방환경청, 국토교통부 부산지방국토관리청, 주식회사 무신사</v>
+        <v>국토교통부 부산지방국토관리청, 기후에너지환경부 원주지방환경청, 나라장터(조달청) 및 기타, 삼환기업(주), 주식회사 무신사</v>
       </c>
       <c r="K1093" t="str">
         <v>B+</v>
@@ -55315,7 +55327,7 @@
         <v>010-8801-6025</v>
       </c>
       <c r="Q1096" t="str">
-        <v>jiwoo0488@hanmail.net</v>
+        <v>jwgroup0488@naver.com</v>
       </c>
     </row>
     <row r="1097">
@@ -55399,6 +55411,9 @@
       <c r="L1098" t="str">
         <v>B</v>
       </c>
+      <c r="M1098" t="str">
+        <v>R-4</v>
+      </c>
       <c r="N1098" t="str">
         <v>대구광역시 수성구</v>
       </c>
@@ -56165,7 +56180,7 @@
         <v>A(CFR1)</v>
       </c>
       <c r="M1113" t="str">
-        <v>NRM2</v>
+        <v>NRM3</v>
       </c>
       <c r="N1113" t="str">
         <v>경기도 수원시</v>
@@ -60615,6 +60630,9 @@
       <c r="L1204" t="str">
         <v>B</v>
       </c>
+      <c r="M1204" t="str">
+        <v>R-4</v>
+      </c>
       <c r="N1204" t="str">
         <v>대구광역시 서구</v>
       </c>
@@ -61365,6 +61383,9 @@
       <c r="L1219" t="str">
         <v>B</v>
       </c>
+      <c r="M1219" t="str">
+        <v>R-4</v>
+      </c>
       <c r="N1219" t="str">
         <v>울산광역시 울주군</v>
       </c>
@@ -62936,7 +62957,7 @@
         <v>B</v>
       </c>
       <c r="M1251" t="str">
-        <v>R-4</v>
+        <v>R-3</v>
       </c>
       <c r="N1251" t="str">
         <v>서울특별시 송파구</v>
@@ -63494,6 +63515,9 @@
       <c r="L1262" t="str">
         <v>C+</v>
       </c>
+      <c r="M1262" t="str">
+        <v>R-4</v>
+      </c>
       <c r="N1262" t="str">
         <v>서울특별시 강남구</v>
       </c>
@@ -63544,6 +63568,9 @@
       <c r="L1263" t="str">
         <v>A</v>
       </c>
+      <c r="M1263" t="str">
+        <v>R-4</v>
+      </c>
       <c r="N1263" t="str">
         <v>경기도 화성시</v>
       </c>
@@ -64692,19 +64719,19 @@
         <v>승강기설치공사업</v>
       </c>
       <c r="J1286" t="str">
-        <v>지에스건설(주), 롯데건설(주), 삼성물산(주), (주)태영건설, (주)에스원</v>
+        <v>용산e편한세상 입주자대표회의, 한화손해보험(주), (주)제일승강기, (주)한화63시티, 서울신용보증재단</v>
       </c>
       <c r="K1286" t="str">
-        <v>BBB-</v>
+        <v>BBB0</v>
       </c>
       <c r="L1286" t="str">
         <v>B</v>
       </c>
       <c r="M1286" t="str">
-        <v>R-3</v>
+        <v>R-2</v>
       </c>
       <c r="N1286" t="str">
-        <v>서울특별시 영등포구</v>
+        <v>서울 영등포구</v>
       </c>
       <c r="O1286" t="str">
         <v>신태인</v>
@@ -70739,6 +70766,9 @@
       </c>
       <c r="L1405" t="str">
         <v>D</v>
+      </c>
+      <c r="M1405" t="str">
+        <v>R-3</v>
       </c>
       <c r="N1405" t="str">
         <v>경상북도 포항시</v>

--- a/data.xlsx
+++ b/data.xlsx
@@ -1377,13 +1377,13 @@
         <v>25년(정규)</v>
       </c>
       <c r="D20">
-        <v>4094</v>
+        <v>4093</v>
       </c>
       <c r="E20">
-        <v>30.496</v>
+        <v>30.5</v>
       </c>
       <c r="F20">
-        <v>4.209</v>
+        <v>4.2</v>
       </c>
       <c r="G20" t="str">
         <v>조경공사</v>
@@ -1395,16 +1395,16 @@
         <v>조경공사업, 조경시설물설치공사업, 조경식재공사업</v>
       </c>
       <c r="J20" t="str">
-        <v>(주)금솔개발, (주)세종종합건설, 금강종합건설(주), 남해군청, 사하구청</v>
+        <v>(주)금솔개발, 경상남도남해군청, 부산광역시사하구청, (주)세종종합건설, 금강종합건설(주)</v>
       </c>
       <c r="K20" t="str">
-        <v>BB0</v>
+        <v>BB+</v>
       </c>
       <c r="L20" t="str">
-        <v>A(CFR1)</v>
+        <v>A</v>
       </c>
       <c r="M20" t="str">
-        <v>NRM3</v>
+        <v>R-2</v>
       </c>
       <c r="N20" t="str">
         <v>부산광역시 강서구</v>
@@ -2894,7 +2894,7 @@
         <v>3058190269</v>
       </c>
       <c r="C51" t="str">
-        <v>입찰제한</v>
+        <v>미승인</v>
       </c>
       <c r="D51">
         <v>2304</v>
@@ -3562,7 +3562,7 @@
         <v>2038154860</v>
       </c>
       <c r="C64" t="str">
-        <v>입찰제한</v>
+        <v>미승인</v>
       </c>
       <c r="D64">
         <v>4409</v>
@@ -7283,13 +7283,13 @@
         <v>25년(정규)</v>
       </c>
       <c r="D138">
-        <v>20673</v>
+        <v>23916</v>
       </c>
       <c r="E138">
-        <v>34.4</v>
+        <v>40.9</v>
       </c>
       <c r="F138">
-        <v>10.6</v>
+        <v>9.5</v>
       </c>
       <c r="G138" t="str">
         <v>조경공사</v>
@@ -7301,13 +7301,13 @@
         <v>조경시설물설치공사업, 조경식재공사업, 포장공사업</v>
       </c>
       <c r="J138" t="str">
-        <v>현대건설(주), 신세계건설(주), (주)금성백조건설, 계룡건설산업(주), 두산건설(주)</v>
+        <v>(주)한화, 계룡건설산업(주), 현대건설(주), 신세계건설(주), (주)금성백조건설</v>
       </c>
       <c r="K138" t="str">
         <v>BB</v>
       </c>
       <c r="L138" t="str">
-        <v>B</v>
+        <v>C-</v>
       </c>
       <c r="M138" t="str">
         <v>R-2</v>
@@ -13151,7 +13151,7 @@
         <v>B</v>
       </c>
       <c r="M255" t="str">
-        <v>R-4</v>
+        <v>R-2</v>
       </c>
       <c r="N255" t="str">
         <v>전라남도 여수시</v>
@@ -13607,7 +13607,7 @@
         <v>B</v>
       </c>
       <c r="M264" t="str">
-        <v>R-3</v>
+        <v>R-2</v>
       </c>
       <c r="N264" t="str">
         <v>전라남도 여수시</v>
@@ -13933,7 +13933,7 @@
         <v>2148846961</v>
       </c>
       <c r="C271" t="str">
-        <v>입찰제한</v>
+        <v>미승인</v>
       </c>
       <c r="D271">
         <v>10065</v>
@@ -13989,25 +13989,25 @@
         <v>25년(예비)</v>
       </c>
       <c r="D272">
-        <v>522</v>
+        <v>1135</v>
       </c>
       <c r="E272">
-        <v>119.118</v>
-      </c>
-      <c r="I272" t="str">
-        <v>용역업</v>
+        <v>149.8</v>
+      </c>
+      <c r="F272">
+        <v>0</v>
       </c>
       <c r="J272" t="str">
-        <v>(주)우방, （주）반도건설, 극동건설(주), 남광토건 주식회사, 주식회사 에이피글로벌(AP Global)</v>
+        <v>(주)에이피글로벌(APGlobal), 극동건설(주), (주)우방, 강릉교동센트럴파크지역주택조합, 경남기업(주)</v>
       </c>
       <c r="K272" t="str">
-        <v>B+(만료)</v>
+        <v>BB-</v>
       </c>
       <c r="L272" t="str">
-        <v>C+(CFR3)(만료)</v>
+        <v>C+</v>
       </c>
       <c r="M272" t="str">
-        <v>NRM4</v>
+        <v>R-3</v>
       </c>
       <c r="N272" t="str">
         <v>인천광역시 서구</v>
@@ -14595,7 +14595,7 @@
         <v>8588600650</v>
       </c>
       <c r="C284" t="str">
-        <v>입찰제한</v>
+        <v>미승인</v>
       </c>
       <c r="D284">
         <v>5530</v>
@@ -15760,13 +15760,13 @@
         <v>25년(정규)</v>
       </c>
       <c r="D307">
-        <v>43593</v>
+        <v>43592</v>
       </c>
       <c r="E307">
-        <v>2726.179</v>
+        <v>2726.2</v>
       </c>
       <c r="F307">
-        <v>40.463</v>
+        <v>40.5</v>
       </c>
       <c r="G307" t="str">
         <v>금속 및 금속창호공사</v>
@@ -15778,16 +15778,13 @@
         <v>지붕판금,건축물조립공사업</v>
       </c>
       <c r="J307" t="str">
-        <v>에스케이에코플랜트 주식회사 (SK ecoplant Co., Ltd.), 동부건설（주）, 현대엔지니어링（주）, 에이치엘디앤아이한라 주식회사, (주)케이씨씨건설</v>
+        <v>에스케이에코플랜트(주), 동부건설(주), 현대엔지니어링(주), 에이치엘디앤아이한라(주), (주)케이씨씨건설</v>
       </c>
       <c r="K307" t="str">
-        <v>BB-</v>
+        <v>B</v>
       </c>
       <c r="L307" t="str">
-        <v>C+(CFR3)</v>
-      </c>
-      <c r="M307" t="str">
-        <v>NRM5</v>
+        <v>C+</v>
       </c>
       <c r="N307" t="str">
         <v>경기도 안양시</v>
@@ -16911,7 +16908,7 @@
         <v>A</v>
       </c>
       <c r="M329" t="str">
-        <v>R-4</v>
+        <v>R-3</v>
       </c>
       <c r="N329" t="str">
         <v>대구광역시 수성구</v>
@@ -17334,13 +17331,13 @@
         <v>25년(정규)</v>
       </c>
       <c r="D338">
-        <v>11614</v>
+        <v>15137</v>
       </c>
       <c r="E338">
-        <v>74.2</v>
+        <v>47.8</v>
       </c>
       <c r="F338">
-        <v>38.3</v>
+        <v>28.2</v>
       </c>
       <c r="G338" t="str">
         <v>도로부대시설공사</v>
@@ -17355,10 +17352,10 @@
         <v>풍림산업(주), 이수건설(주), 삼환기업(주), 쌍용건설(주), 부산-김해경전철(주)</v>
       </c>
       <c r="K338" t="str">
-        <v>BB-</v>
+        <v>BB+</v>
       </c>
       <c r="L338" t="str">
-        <v>C-</v>
+        <v>C+</v>
       </c>
       <c r="M338" t="str">
         <v>R-4</v>
@@ -18504,6 +18501,9 @@
       <c r="L361" t="str">
         <v>A</v>
       </c>
+      <c r="M361" t="str">
+        <v>R-2</v>
+      </c>
       <c r="N361" t="str">
         <v>서울특별시 강남구</v>
       </c>
@@ -18772,10 +18772,7 @@
         <v>25년(예비)</v>
       </c>
       <c r="D367">
-        <v>1428</v>
-      </c>
-      <c r="E367">
-        <v>28.7</v>
+        <v>1436</v>
       </c>
       <c r="J367" t="str">
         <v>（주）남광석재, 경남기업（주), 대보건설 주식회사, 동광건설 주식회사, 주식회사 삼정이앤시</v>
@@ -21104,7 +21101,7 @@
         <v>1318800016</v>
       </c>
       <c r="C414" t="str">
-        <v>입찰제한</v>
+        <v>미승인</v>
       </c>
       <c r="D414">
         <v>7414</v>
@@ -22307,7 +22304,7 @@
         <v>2148830983</v>
       </c>
       <c r="C438" t="str">
-        <v>입찰제한</v>
+        <v>미승인</v>
       </c>
       <c r="D438">
         <v>13176</v>
@@ -23225,7 +23222,7 @@
         <v>2238109961</v>
       </c>
       <c r="C456" t="str">
-        <v>입찰제한</v>
+        <v>미승인</v>
       </c>
       <c r="D456">
         <v>6801</v>
@@ -32351,7 +32348,7 @@
         <v>금속구조물,창호공사업, 지붕판금,건축물조립공사업</v>
       </c>
       <c r="J639" t="str">
-        <v>여수시청, 남광토건 주식회사, 금광기업（주）, 경기도용인교육지원청, 의왕시청</v>
+        <v>경기도용인교육지원청, 금광기업（주）, 남광토건 주식회사, 여수시청, 의왕시청</v>
       </c>
       <c r="K639" t="str">
         <v>BB-</v>
@@ -32383,7 +32380,7 @@
         <v>6108132273</v>
       </c>
       <c r="C640" t="str">
-        <v>입찰제한</v>
+        <v>미승인</v>
       </c>
       <c r="D640">
         <v>2912</v>
@@ -32872,13 +32869,13 @@
         <v>금속구조물,창호공사업, 기계설비공사업</v>
       </c>
       <c r="J649" t="str">
-        <v>(주)포스코이앤씨, 금호건설 주식회사, 디원랩(D1_LAB), 에스앤티에너지 주식회사, 주식회사 제이엔텍</v>
+        <v>(주)다원산업개발, (주)포스코건설, 금호산업(주), 에스앤티에너지(주)</v>
       </c>
       <c r="K649" t="str">
-        <v>BB+(만료)</v>
+        <v>BB0</v>
       </c>
       <c r="L649" t="str">
-        <v>C+(CFR3)(만료)</v>
+        <v>C+(CFR3)</v>
       </c>
       <c r="M649" t="str">
         <v>NRM4</v>
@@ -36131,7 +36128,7 @@
         <v>6218177848</v>
       </c>
       <c r="C714" t="str">
-        <v>입찰제한</v>
+        <v>미승인</v>
       </c>
       <c r="D714">
         <v>4507</v>
@@ -46066,7 +46063,7 @@
         <v>1118133775</v>
       </c>
       <c r="C913" t="str">
-        <v>입찰제한</v>
+        <v>미승인</v>
       </c>
       <c r="D913">
         <v>24351</v>
@@ -46881,7 +46878,7 @@
         <v>3038154286</v>
       </c>
       <c r="C929" t="str">
-        <v>입찰제한</v>
+        <v>미승인</v>
       </c>
       <c r="D929">
         <v>44097</v>
@@ -47193,7 +47190,7 @@
         <v>6158170758</v>
       </c>
       <c r="C935" t="str">
-        <v>입찰제한</v>
+        <v>미승인</v>
       </c>
       <c r="D935">
         <v>11245</v>
@@ -50794,10 +50791,10 @@
         <v>(주)케이씨씨건설, (주)포스코이앤씨, 한국토지주택공사 인천지역본부, 에이치디씨현대산업개발 주식회사, 삼성물산 (주)</v>
       </c>
       <c r="K1006" t="str">
-        <v>D</v>
+        <v>D(만료)</v>
       </c>
       <c r="L1006" t="str">
-        <v>NF</v>
+        <v>NF(만료)</v>
       </c>
       <c r="M1006" t="str">
         <v>NRM7</v>
@@ -53315,7 +53312,7 @@
         <v>2168105614</v>
       </c>
       <c r="C1056" t="str">
-        <v>입찰제한</v>
+        <v>미승인</v>
       </c>
       <c r="D1056">
         <v>6908</v>
@@ -58497,7 +58494,7 @@
         <v>4168106232</v>
       </c>
       <c r="C1160" t="str">
-        <v>입찰제한</v>
+        <v>미승인</v>
       </c>
       <c r="D1160">
         <v>51743</v>
@@ -59746,7 +59743,7 @@
         <v>B</v>
       </c>
       <c r="M1186" t="str">
-        <v>R-4</v>
+        <v>R-3</v>
       </c>
       <c r="N1186" t="str">
         <v>대구광역시 수성구</v>
@@ -62527,6 +62524,9 @@
       <c r="L1242" t="str">
         <v>A</v>
       </c>
+      <c r="M1242" t="str">
+        <v>R-1</v>
+      </c>
       <c r="N1242" t="str">
         <v>경기도 김포시</v>
       </c>
@@ -64701,10 +64701,10 @@
         <v>25년(정규)</v>
       </c>
       <c r="D1286">
-        <v>263262</v>
+        <v>245760</v>
       </c>
       <c r="E1286">
-        <v>146.3</v>
+        <v>120.9</v>
       </c>
       <c r="F1286">
         <v>0</v>
@@ -64719,19 +64719,19 @@
         <v>승강기설치공사업</v>
       </c>
       <c r="J1286" t="str">
-        <v>용산e편한세상 입주자대표회의, 한화손해보험(주), (주)제일승강기, (주)한화63시티, 서울신용보증재단</v>
+        <v>삼성물산(주), 롯데건설(주), (주)포스코이앤씨, (주)에스원, 지에스건설(주)</v>
       </c>
       <c r="K1286" t="str">
-        <v>BBB0</v>
+        <v>BBB</v>
       </c>
       <c r="L1286" t="str">
-        <v>B</v>
+        <v>C+</v>
       </c>
       <c r="M1286" t="str">
-        <v>R-2</v>
+        <v>R-3</v>
       </c>
       <c r="N1286" t="str">
-        <v>서울 영등포구</v>
+        <v>서울특별시 영등포구</v>
       </c>
       <c r="O1286" t="str">
         <v>신태인</v>
@@ -67307,7 +67307,7 @@
         <v>1128125375</v>
       </c>
       <c r="C1338" t="str">
-        <v>입찰제한</v>
+        <v>미승인</v>
       </c>
       <c r="D1338">
         <v>4343</v>
@@ -68172,7 +68172,7 @@
         <v>1398100495</v>
       </c>
       <c r="C1355" t="str">
-        <v>입찰제한</v>
+        <v>미승인</v>
       </c>
       <c r="D1355">
         <v>6845</v>
